--- a/artfynd/A 60543-2023 artfynd.xlsx
+++ b/artfynd/A 60543-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60543-2023 artfynd.xlsx
+++ b/artfynd/A 60543-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>63742665</v>
       </c>
       <c r="B2" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98608</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>424606.117622979</v>
+        <v>424606</v>
       </c>
       <c r="R2" t="n">
-        <v>6160296.975692132</v>
+        <v>6160297</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1998-08-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1998-08-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -809,12 +794,7 @@
         <v>63742666</v>
       </c>
       <c r="B3" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98918</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -846,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>424606.117622979</v>
+        <v>424606</v>
       </c>
       <c r="R3" t="n">
-        <v>6160296.975692132</v>
+        <v>6160297</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -879,19 +859,9 @@
           <t>1998-08-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1998-08-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -940,12 +910,7 @@
         <v>63742780</v>
       </c>
       <c r="B4" t="n">
-        <v>105928</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108366</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>424606.117622979</v>
+        <v>424606</v>
       </c>
       <c r="R4" t="n">
-        <v>6160296.975692132</v>
+        <v>6160297</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1010,19 +975,9 @@
           <t>2000-06-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2000-06-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1046,7 +1001,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Lund-Botaniska/Zoologiska museet</t>
+          <t>Biologiska Museet, Lunds Universitet</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1076,12 +1031,7 @@
         <v>63742664</v>
       </c>
       <c r="B5" t="n">
-        <v>101325</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103662</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>424606.117622979</v>
+        <v>424606</v>
       </c>
       <c r="R5" t="n">
-        <v>6160296.975692132</v>
+        <v>6160297</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1146,19 +1096,9 @@
           <t>1998-08-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1998-08-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/artfynd/A 60543-2023 artfynd.xlsx
+++ b/artfynd/A 60543-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63742665</v>
       </c>
       <c r="B2" t="n">
-        <v>98669</v>
+        <v>98674</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63742666</v>
       </c>
       <c r="B3" t="n">
-        <v>98980</v>
+        <v>98985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>63742780</v>
       </c>
       <c r="B4" t="n">
-        <v>108449</v>
+        <v>108454</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>63742664</v>
       </c>
       <c r="B5" t="n">
-        <v>103738</v>
+        <v>103743</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60543-2023 artfynd.xlsx
+++ b/artfynd/A 60543-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63742665</v>
       </c>
       <c r="B2" t="n">
-        <v>98674</v>
+        <v>98682</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63742666</v>
       </c>
       <c r="B3" t="n">
-        <v>98985</v>
+        <v>98993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>63742780</v>
       </c>
       <c r="B4" t="n">
-        <v>108454</v>
+        <v>108462</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>63742664</v>
       </c>
       <c r="B5" t="n">
-        <v>103743</v>
+        <v>103751</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60543-2023 artfynd.xlsx
+++ b/artfynd/A 60543-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63742665</v>
       </c>
       <c r="B2" t="n">
-        <v>98682</v>
+        <v>98692</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63742666</v>
       </c>
       <c r="B3" t="n">
-        <v>98993</v>
+        <v>99003</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>63742780</v>
       </c>
       <c r="B4" t="n">
-        <v>108462</v>
+        <v>108472</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>63742664</v>
       </c>
       <c r="B5" t="n">
-        <v>103751</v>
+        <v>103761</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60543-2023 artfynd.xlsx
+++ b/artfynd/A 60543-2023 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>63742780</v>
       </c>
       <c r="B4" t="n">
-        <v>108472</v>
+        <v>108781</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60543-2023 artfynd.xlsx
+++ b/artfynd/A 60543-2023 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>63742780</v>
       </c>
       <c r="B4" t="n">
-        <v>108781</v>
+        <v>108795</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60543-2023 artfynd.xlsx
+++ b/artfynd/A 60543-2023 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>63742780</v>
       </c>
       <c r="B4" t="n">
-        <v>108795</v>
+        <v>108833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60543-2023 artfynd.xlsx
+++ b/artfynd/A 60543-2023 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>63742780</v>
       </c>
       <c r="B4" t="n">
-        <v>108833</v>
+        <v>108847</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60543-2023 artfynd.xlsx
+++ b/artfynd/A 60543-2023 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>63742780</v>
       </c>
       <c r="B4" t="n">
-        <v>108869</v>
+        <v>108870</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60543-2023 artfynd.xlsx
+++ b/artfynd/A 60543-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63742665</v>
       </c>
       <c r="B2" t="n">
-        <v>98692</v>
+        <v>99142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63742666</v>
       </c>
       <c r="B3" t="n">
-        <v>99003</v>
+        <v>99456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,38 +907,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>63742780</v>
+        <v>63742664</v>
       </c>
       <c r="B4" t="n">
-        <v>108870</v>
+        <v>104254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>231856</v>
+        <v>222056</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trollfibbla</t>
+          <t>Stor häxört</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hieracium oistophyllum</t>
+          <t>Circaea lutetiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pugsley</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>N Eriksdalsverken, Sk</t>
+          <t>Eriksdal, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -972,17 +972,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2000-06-03</t>
+          <t>1998-08-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2000-06-03</t>
+          <t>1998-08-02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hieracium sagittatum/2D2e3338/Röddinge s:n/ÅSv/ (H. oistorphyllum) även 8027,8030,8029  /Åke Svensson,Knislinge</t>
+          <t>Circaea lutetiana/2D2e3338/Röddinge s:n/ÅSv/ /Åke Svensson,Knislinge</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,17 +996,12 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>bokskogssluttning</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>Biologiska Museet, Lunds Universitet</t>
+          <t>i lövskog vid bäck</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>SkFlora    708582</t>
+          <t>SkFlora    462320</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1028,38 +1023,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>63742664</v>
+        <v>63742780</v>
       </c>
       <c r="B5" t="n">
-        <v>103761</v>
+        <v>109003</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222056</v>
+        <v>231856</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor häxört</t>
+          <t>Trollfibbla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Circaea lutetiana</t>
+          <t>Hieracium oistophyllum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pugsley</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Eriksdal, Sk</t>
+          <t>N Eriksdalsverken, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1093,17 +1088,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1998-08-02</t>
+          <t>2000-06-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1998-08-02</t>
+          <t>2000-06-03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Circaea lutetiana/2D2e3338/Röddinge s:n/ÅSv/ /Åke Svensson,Knislinge</t>
+          <t>Hieracium sagittatum/2D2e3338/Röddinge s:n/ÅSv/ (H. oistorphyllum) även 8027,8030,8029  /Åke Svensson,Knislinge</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,12 +1112,17 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>i lövskog vid bäck</t>
+          <t>bokskogssluttning</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Biologiska Museet, Lunds Universitet</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>SkFlora    462320</t>
+          <t>SkFlora    708582</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
